--- a/synthetic/documents/xlsx/order_107_NMC-01106.xlsx
+++ b/synthetic/documents/xlsx/order_107_NMC-01106.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -511,88 +511,71 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Date:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>FST-HCS-M10-4</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Hex Cap Screw M10 x 4 Grade 5 Zinc (SYNTHETIC)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>BX</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>830.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ATLAS-ABR-6621</t>
+          <t>FST-HCS-M10-4</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Cut-Off Wheel 6in (SYNTHETIC)</t>
+          <t>Hex Cap Screw M10 x 4 Grade 5 Zinc (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -600,53 +583,53 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>47.08</v>
+        <v>34.62</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>188.32</v>
+        <v>830.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PKG-STW-097</t>
+          <t>ATLAS-ABR-6621</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Stretch Wrap 18in (SYNTHETIC)</t>
+          <t>Cut-Off Wheel 6in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>115.67</v>
+        <v>47.08</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>115.67</v>
+        <v>188.32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ATLAS-JAN-2032</t>
+          <t>PKG-STW-097</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Floor Pad 17in White (SYNTHETIC)</t>
+          <t>Stretch Wrap 18in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -658,38 +641,67 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>36.81</v>
+        <v>115.67</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>36.81</v>
+        <v>115.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ATLAS-JAN-2032</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Floor Pad 17in White (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>36.81</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>ATLAS-JAN-8673</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Floor Cleaner Neutral Concentrate (SYNTHETIC)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>58.32</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>699.84</v>
       </c>
     </row>
